--- a/docs/downloads/05/tbl_water_alaotra_ambohidrony.xlsx
+++ b/docs/downloads/05/tbl_water_alaotra_ambohidrony.xlsx
@@ -544,12 +544,6 @@
           <t>Alaotra - Tous</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.2</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
